--- a/data/externalStats/File2/TC1924_Exc_External.xlsx
+++ b/data/externalStats/File2/TC1924_Exc_External.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ms.ds.uhc.com\userdata\030\amitta73\Desktop\RPT_Automation\data\externalStats\File2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80B39E6A-EF11-49E9-8D8C-9F76E9CD9382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3A367E9-7C19-4334-BD6B-62BE7B5D9EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{542964DF-F7C1-4D18-B052-55F3EAB03B6B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{51922749-857A-4272-A175-5C4265852E0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="123">
   <si>
     <t>General Dynamics</t>
   </si>
@@ -107,6 +107,9 @@
     <t>Retail 90</t>
   </si>
   <si>
+    <t>OZEMPIC</t>
+  </si>
+  <si>
     <t>XOLAIR</t>
   </si>
   <si>
@@ -116,7 +119,10 @@
     <t>Mail</t>
   </si>
   <si>
-    <t>OZEMPIC</t>
+    <t>JARDIANCE</t>
+  </si>
+  <si>
+    <t>SGLT-2 INHIBITORS &amp; COMBOS</t>
   </si>
   <si>
     <t>FOLLISTIM AQ</t>
@@ -128,10 +134,10 @@
     <t>Non-Specialty</t>
   </si>
   <si>
-    <t>JARDIANCE</t>
-  </si>
-  <si>
-    <t>SGLT-2 INHIBITORS &amp; COMBOS</t>
+    <t>DEXCOM G7 SENSOR</t>
+  </si>
+  <si>
+    <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
   </si>
   <si>
     <t>BIKTARVY</t>
@@ -143,10 +149,10 @@
     <t>Specialty</t>
   </si>
   <si>
-    <t>DEXCOM G7 SENSOR</t>
-  </si>
-  <si>
-    <t>DIABETES MONITORING AND TESTING SUPPLIES</t>
+    <t>NURTEC</t>
+  </si>
+  <si>
+    <t>MIGRAINE PRODUCTS</t>
   </si>
   <si>
     <t>TEZSPIRE</t>
@@ -155,10 +161,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>NURTEC</t>
-  </si>
-  <si>
-    <t>MIGRAINE PRODUCTS</t>
+    <t>DEXCOM G6 SENSOR</t>
   </si>
   <si>
     <t>WAKIX</t>
@@ -167,7 +170,10 @@
     <t>NARCOLEPSY</t>
   </si>
   <si>
-    <t>DEXCOM G6 SENSOR</t>
+    <t>ELIQUIS</t>
+  </si>
+  <si>
+    <t>ORAL ANTICOAGULANTS</t>
   </si>
   <si>
     <t>JAKAFI</t>
@@ -179,10 +185,10 @@
     <t>Generic</t>
   </si>
   <si>
-    <t>ELIQUIS</t>
-  </si>
-  <si>
-    <t>ORAL ANTICOAGULANTS</t>
+    <t>SKYRIZI PEN</t>
+  </si>
+  <si>
+    <t>IMMUNOMODULATORS</t>
   </si>
   <si>
     <t>OXERVATE</t>
@@ -191,10 +197,7 @@
     <t>OPHTHALMIC NERVE GROWTH FACTORS</t>
   </si>
   <si>
-    <t>SKYRIZI PEN</t>
-  </si>
-  <si>
-    <t>IMMUNOMODULATORS</t>
+    <t>QULIPTA</t>
   </si>
   <si>
     <t>HEMLIBRA</t>
@@ -203,7 +206,7 @@
     <t>ANTIHEMOPHILIC PRODUCTS</t>
   </si>
   <si>
-    <t>QULIPTA</t>
+    <t>XYWAV</t>
   </si>
   <si>
     <t>VYNDAMAX</t>
@@ -212,7 +215,7 @@
     <t>TRANSTHYRETIN STABILIZERS</t>
   </si>
   <si>
-    <t>XYWAV</t>
+    <t>TRULICITY</t>
   </si>
   <si>
     <t>NGENLA</t>
@@ -221,7 +224,10 @@
     <t>GROWTH HORMONES</t>
   </si>
   <si>
-    <t>TRULICITY</t>
+    <t>TRELEGY ELLIPTA</t>
+  </si>
+  <si>
+    <t>LABA LAMA COMBO</t>
   </si>
   <si>
     <t>BIMZELX</t>
@@ -230,10 +236,7 @@
     <t>CHRONIC INFLAMMATORY DISEASE</t>
   </si>
   <si>
-    <t>TRELEGY ELLIPTA</t>
-  </si>
-  <si>
-    <t>LABA LAMA COMBO</t>
+    <t>AJOVY</t>
   </si>
   <si>
     <t>BENLYSTA</t>
@@ -242,7 +245,7 @@
     <t>LUPUS AGENT</t>
   </si>
   <si>
-    <t>AJOVY</t>
+    <t>HUMIRA PEN</t>
   </si>
   <si>
     <t>EVRYSDI</t>
@@ -251,13 +254,16 @@
     <t>SPINAL MUSCULAR ATROPHY (SMA) AGENT</t>
   </si>
   <si>
-    <t>HUMIRA PEN</t>
+    <t>UBRELVY</t>
   </si>
   <si>
     <t>NUCALA</t>
   </si>
   <si>
-    <t>UBRELVY</t>
+    <t>OMNIPOD 5 DEXCOM G7G6 PODS (GEN 5)</t>
+  </si>
+  <si>
+    <t>INSULIN ADMINISTRATION SUPPLIES</t>
   </si>
   <si>
     <t>PROCYSBI</t>
@@ -266,10 +272,7 @@
     <t>ENDOCRINE DISORDERS</t>
   </si>
   <si>
-    <t>OMNIPOD 5 DEXCOM G7G6 PODS (GEN 5)</t>
-  </si>
-  <si>
-    <t>INSULIN ADMINISTRATION SUPPLIES</t>
+    <t>RYBELSUS</t>
   </si>
   <si>
     <t>SPRAVATO 84MG DOSE</t>
@@ -278,25 +281,25 @@
     <t>ANTIDEPRESSANTS</t>
   </si>
   <si>
-    <t>RYBELSUS</t>
+    <t>REPATHA SURECLICK</t>
+  </si>
+  <si>
+    <t>PCSK9 INHIBITORS</t>
   </si>
   <si>
     <t>REVLIMID</t>
   </si>
   <si>
-    <t>REPATHA SURECLICK</t>
-  </si>
-  <si>
-    <t>PCSK9 INHIBITORS</t>
+    <t>LINZESS</t>
+  </si>
+  <si>
+    <t>IRRITABLE BOWEL SYNDROME (IBS) AGENTS</t>
   </si>
   <si>
     <t>ARCALYST</t>
   </si>
   <si>
-    <t>LINZESS</t>
-  </si>
-  <si>
-    <t>IRRITABLE BOWEL SYNDROME (IBS) AGENTS</t>
+    <t>AIMOVIG</t>
   </si>
   <si>
     <t>IMBRUVICA</t>
@@ -772,7 +775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DE8DAD-C2B4-4A7C-88B8-CCDD63199446}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFD0F26F-F928-40B6-AE32-618A896131B3}">
   <dimension ref="A15:AN129"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -935,25 +938,25 @@
         <v>2</v>
       </c>
       <c r="AF26" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AG26" t="s">
         <v>19</v>
       </c>
       <c r="AH26">
-        <v>28322295.490262493</v>
+        <v>11053681.775939891</v>
       </c>
       <c r="AI26">
-        <v>37843.664796758472</v>
+        <v>14824.518697908357</v>
       </c>
       <c r="AK26">
         <v>2</v>
       </c>
       <c r="AL26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN26">
         <v>0</v>
@@ -961,7 +964,7 @@
     </row>
     <row r="27" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27">
         <v>7339</v>
@@ -982,25 +985,25 @@
         <v>3</v>
       </c>
       <c r="AF27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AH27">
-        <v>11053681.775939891</v>
+        <v>10284229.207468122</v>
       </c>
       <c r="AI27">
-        <v>14824.518697908357</v>
+        <v>12396.815951838802</v>
       </c>
       <c r="AK27">
         <v>3</v>
       </c>
       <c r="AL27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AM27" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AN27">
         <v>11.400168300000001</v>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="28" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28">
         <v>142187</v>
@@ -1029,25 +1032,25 @@
         <v>4</v>
       </c>
       <c r="AF28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AH28">
-        <v>10284229.207468122</v>
+        <v>5120351.540857112</v>
       </c>
       <c r="AI28">
-        <v>12396.815951838802</v>
+        <v>0</v>
       </c>
       <c r="AK28">
         <v>4</v>
       </c>
       <c r="AL28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM28" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AN28">
         <v>0</v>
@@ -1055,7 +1058,7 @@
     </row>
     <row r="29" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29">
         <v>4332</v>
@@ -1076,25 +1079,25 @@
         <v>5</v>
       </c>
       <c r="AF29" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AG29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AH29">
-        <v>5120351.540857112</v>
+        <v>2870215.2227192577</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>2997.0371922737795</v>
       </c>
       <c r="AK29">
         <v>5</v>
       </c>
       <c r="AL29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AM29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN29">
         <v>0</v>
@@ -1102,7 +1105,7 @@
     </row>
     <row r="30" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D30">
         <v>146519</v>
@@ -1123,25 +1126,25 @@
         <v>6</v>
       </c>
       <c r="AF30" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AG30" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AH30">
-        <v>2870215.2227192577</v>
+        <v>2681546.565749675</v>
       </c>
       <c r="AI30">
-        <v>2997.0371922737795</v>
+        <v>0</v>
       </c>
       <c r="AK30">
         <v>6</v>
       </c>
       <c r="AL30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AM30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AN30">
         <v>0</v>
@@ -1152,25 +1155,25 @@
         <v>7</v>
       </c>
       <c r="AF31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AG31" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="AH31">
-        <v>2681546.565749675</v>
+        <v>2101412.2256452884</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>5564.4421249999987</v>
       </c>
       <c r="AK31">
         <v>7</v>
       </c>
       <c r="AL31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM31" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AN31">
         <v>36.265829600000004</v>
@@ -1178,31 +1181,31 @@
     </row>
     <row r="32" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE32">
         <v>8</v>
       </c>
       <c r="AF32" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AG32" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AH32">
-        <v>2101412.2256452884</v>
+        <v>1970838.704334199</v>
       </c>
       <c r="AI32">
-        <v>5564.4421249999987</v>
+        <v>158.29228499999999</v>
       </c>
       <c r="AK32">
         <v>8</v>
       </c>
       <c r="AL32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AM32" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AN32">
         <v>0</v>
@@ -1231,25 +1234,25 @@
         <v>9</v>
       </c>
       <c r="AF33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AG33" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="AH33">
-        <v>1970838.704334199</v>
+        <v>1941215.8959066484</v>
       </c>
       <c r="AI33">
-        <v>158.29228499999999</v>
+        <v>2057.3407889999999</v>
       </c>
       <c r="AK33">
         <v>9</v>
       </c>
       <c r="AL33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AM33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AN33">
         <v>0</v>
@@ -1278,25 +1281,25 @@
         <v>10</v>
       </c>
       <c r="AF34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AG34" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AH34">
-        <v>1941215.8959066484</v>
+        <v>1789477.8068682214</v>
       </c>
       <c r="AI34">
-        <v>2057.3407889999999</v>
+        <v>307.20835685871339</v>
       </c>
       <c r="AK34">
         <v>10</v>
       </c>
       <c r="AL34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AM34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AN34">
         <v>0</v>
@@ -1304,7 +1307,7 @@
     </row>
     <row r="35" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D35">
         <v>55166</v>
@@ -1325,25 +1328,25 @@
         <v>11</v>
       </c>
       <c r="AF35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AG35" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="AH35">
-        <v>1789477.8068682214</v>
+        <v>1789465.390993749</v>
       </c>
       <c r="AI35">
-        <v>307.20835685871339</v>
+        <v>2313.1288366777553</v>
       </c>
       <c r="AK35">
         <v>11</v>
       </c>
       <c r="AL35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AM35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN35">
         <v>0</v>
@@ -1351,7 +1354,7 @@
     </row>
     <row r="36" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D36">
         <v>1372625</v>
@@ -1372,25 +1375,25 @@
         <v>12</v>
       </c>
       <c r="AF36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AG36" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="AH36">
-        <v>1789465.390993749</v>
+        <v>1571920.2253772859</v>
       </c>
       <c r="AI36">
-        <v>2313.1288366777553</v>
+        <v>3118.8076070000002</v>
       </c>
       <c r="AK36">
         <v>12</v>
       </c>
       <c r="AL36" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AM36" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AN36">
         <v>0</v>
@@ -1398,7 +1401,7 @@
     </row>
     <row r="37" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D37">
         <v>103</v>
@@ -1419,25 +1422,25 @@
         <v>13</v>
       </c>
       <c r="AF37" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AG37" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AH37">
-        <v>1571920.2253772859</v>
+        <v>1408907.5903049174</v>
       </c>
       <c r="AI37">
-        <v>3118.8076070000002</v>
+        <v>1821.6714885051624</v>
       </c>
       <c r="AK37">
         <v>13</v>
       </c>
       <c r="AL37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AM37" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AN37">
         <v>35.310747999999997</v>
@@ -1445,7 +1448,7 @@
     </row>
     <row r="38" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D38">
         <v>1372728</v>
@@ -1466,25 +1469,25 @@
         <v>14</v>
       </c>
       <c r="AF38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG38" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AH38">
-        <v>1408907.5903049174</v>
+        <v>1401603.0325464765</v>
       </c>
       <c r="AI38">
-        <v>1821.6714885051624</v>
+        <v>187.22145737482552</v>
       </c>
       <c r="AK38">
         <v>14</v>
       </c>
       <c r="AL38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AM38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AN38">
         <v>0</v>
@@ -1495,25 +1498,25 @@
         <v>15</v>
       </c>
       <c r="AF39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG39" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="AH39">
-        <v>1401603.0325464765</v>
+        <v>1298529.249782912</v>
       </c>
       <c r="AI39">
-        <v>187.22145737482552</v>
+        <v>2216.3441933262202</v>
       </c>
       <c r="AK39">
         <v>15</v>
       </c>
       <c r="AL39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AM39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN39">
         <v>0</v>
@@ -1521,31 +1524,31 @@
     </row>
     <row r="40" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE40">
         <v>16</v>
       </c>
       <c r="AF40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AG40" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AH40">
-        <v>1298529.249782912</v>
+        <v>1286600.0713925867</v>
       </c>
       <c r="AI40">
-        <v>2216.3441933262202</v>
+        <v>0</v>
       </c>
       <c r="AK40">
         <v>16</v>
       </c>
       <c r="AL40" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AM40" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AN40">
         <v>0</v>
@@ -1574,25 +1577,25 @@
         <v>17</v>
       </c>
       <c r="AF41" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AG41" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="AH41">
-        <v>1286600.0713925867</v>
+        <v>1201949.9257162621</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>1336.8151135625706</v>
       </c>
       <c r="AK41">
         <v>17</v>
       </c>
       <c r="AL41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN41">
         <v>120.543588</v>
@@ -1621,25 +1624,25 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG42" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="AH42">
-        <v>1201949.9257162621</v>
+        <v>1156515.4146088178</v>
       </c>
       <c r="AI42">
-        <v>1336.8151135625706</v>
+        <v>2777.6427869999998</v>
       </c>
       <c r="AK42">
         <v>18</v>
       </c>
       <c r="AL42" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AM42" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AN42">
         <v>5.6898328476059561</v>
@@ -1647,7 +1650,7 @@
     </row>
     <row r="43" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D43">
         <v>62505</v>
@@ -1668,25 +1671,25 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AG43" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AH43">
-        <v>1156515.4146088178</v>
+        <v>1132861.2225870474</v>
       </c>
       <c r="AI43">
-        <v>2777.6427869999998</v>
+        <v>2577.6153793737381</v>
       </c>
       <c r="AK43">
         <v>19</v>
       </c>
       <c r="AL43" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AM43" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AN43">
         <v>0</v>
@@ -1694,7 +1697,7 @@
     </row>
     <row r="44" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D44">
         <v>1514812</v>
@@ -1715,25 +1718,25 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG44" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="AH44">
-        <v>1132861.2225870474</v>
+        <v>1035027.5470974531</v>
       </c>
       <c r="AI44">
-        <v>2577.6153793737381</v>
+        <v>1651.0133282948379</v>
       </c>
       <c r="AK44">
         <v>20</v>
       </c>
       <c r="AL44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AM44" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AN44">
         <v>0</v>
@@ -1741,7 +1744,7 @@
     </row>
     <row r="45" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D45">
         <v>4435</v>
@@ -1761,7 +1764,7 @@
     </row>
     <row r="46" spans="2:40" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D46">
         <v>1519247</v>
@@ -1781,7 +1784,7 @@
     </row>
     <row r="47" spans="2:40" x14ac:dyDescent="0.35">
       <c r="AE47" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="2:40" x14ac:dyDescent="0.35">
@@ -1795,7 +1798,7 @@
         <v>15</v>
       </c>
       <c r="AH48" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="2:34" x14ac:dyDescent="0.35">
@@ -1817,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="AF50" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="AG50">
         <v>11262724.908179237</v>
@@ -1828,7 +1831,7 @@
     </row>
     <row r="51" spans="2:34" x14ac:dyDescent="0.35">
       <c r="D51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J51">
         <v>2027</v>
@@ -1843,7 +1846,7 @@
         <v>3</v>
       </c>
       <c r="AF51" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG51">
         <v>8567448.9019225463</v>
@@ -1854,73 +1857,73 @@
     </row>
     <row r="52" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E52" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" t="s">
+        <v>36</v>
+      </c>
+      <c r="H52" t="s">
+        <v>40</v>
+      </c>
+      <c r="J52" t="s">
         <v>93</v>
       </c>
-      <c r="F52" t="s">
-        <v>25</v>
-      </c>
-      <c r="G52" t="s">
-        <v>34</v>
-      </c>
-      <c r="H52" t="s">
-        <v>38</v>
-      </c>
-      <c r="J52" t="s">
-        <v>92</v>
-      </c>
       <c r="K52" t="s">
+        <v>94</v>
+      </c>
+      <c r="L52" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" t="s">
+        <v>36</v>
+      </c>
+      <c r="N52" t="s">
+        <v>40</v>
+      </c>
+      <c r="P52" t="s">
         <v>93</v>
       </c>
-      <c r="L52" t="s">
-        <v>25</v>
-      </c>
-      <c r="M52" t="s">
-        <v>34</v>
-      </c>
-      <c r="N52" t="s">
-        <v>38</v>
-      </c>
-      <c r="P52" t="s">
-        <v>92</v>
-      </c>
       <c r="Q52" t="s">
+        <v>94</v>
+      </c>
+      <c r="R52" t="s">
+        <v>26</v>
+      </c>
+      <c r="S52" t="s">
+        <v>36</v>
+      </c>
+      <c r="T52" t="s">
+        <v>40</v>
+      </c>
+      <c r="V52" t="s">
         <v>93</v>
       </c>
-      <c r="R52" t="s">
-        <v>25</v>
-      </c>
-      <c r="S52" t="s">
-        <v>34</v>
-      </c>
-      <c r="T52" t="s">
-        <v>38</v>
-      </c>
-      <c r="V52" t="s">
-        <v>92</v>
-      </c>
       <c r="W52" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y52" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z52" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE52">
         <v>4</v>
       </c>
       <c r="AF52" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="AG52">
         <v>8284801.9617493674</v>
@@ -1931,7 +1934,7 @@
     </row>
     <row r="53" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -1997,7 +2000,7 @@
         <v>5</v>
       </c>
       <c r="AF53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AG53">
         <v>6254997.3888322692</v>
@@ -2008,7 +2011,7 @@
     </row>
     <row r="54" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D54">
         <v>18999</v>
@@ -2074,7 +2077,7 @@
         <v>6</v>
       </c>
       <c r="AF54" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AG54">
         <v>3525246.2654963853</v>
@@ -2085,7 +2088,7 @@
     </row>
     <row r="55" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2151,7 +2154,7 @@
         <v>7</v>
       </c>
       <c r="AF55" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AG55">
         <v>2558791.4414515034</v>
@@ -2162,7 +2165,7 @@
     </row>
     <row r="56" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2228,7 +2231,7 @@
         <v>8</v>
       </c>
       <c r="AF56" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AG56">
         <v>2077858.3369724848</v>
@@ -2239,7 +2242,7 @@
     </row>
     <row r="57" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2305,7 +2308,7 @@
         <v>9</v>
       </c>
       <c r="AF57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG57">
         <v>1652160.9353435463</v>
@@ -2316,7 +2319,7 @@
     </row>
     <row r="58" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D58">
         <v>2751</v>
@@ -2382,7 +2385,7 @@
         <v>10</v>
       </c>
       <c r="AF58" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AG58">
         <v>1394375.389541361</v>
@@ -2393,7 +2396,7 @@
     </row>
     <row r="59" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2459,7 +2462,7 @@
         <v>11</v>
       </c>
       <c r="AF59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG59">
         <v>1197548.5028810271</v>
@@ -2470,7 +2473,7 @@
     </row>
     <row r="60" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2536,7 +2539,7 @@
         <v>12</v>
       </c>
       <c r="AF60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AG60">
         <v>1196953.1303542196</v>
@@ -2547,7 +2550,7 @@
     </row>
     <row r="61" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2613,7 +2616,7 @@
         <v>13</v>
       </c>
       <c r="AF61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG61">
         <v>1007293.2425328295</v>
@@ -2624,7 +2627,7 @@
     </row>
     <row r="62" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D62">
         <v>207</v>
@@ -2690,7 +2693,7 @@
         <v>14</v>
       </c>
       <c r="AF62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG62">
         <v>989013.90751893015</v>
@@ -2701,7 +2704,7 @@
     </row>
     <row r="63" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D63">
         <v>3161</v>
@@ -2767,7 +2770,7 @@
         <v>15</v>
       </c>
       <c r="AF63" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG63">
         <v>880391.17035533348</v>
@@ -2778,7 +2781,7 @@
     </row>
     <row r="64" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2844,7 +2847,7 @@
         <v>16</v>
       </c>
       <c r="AF64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AG64">
         <v>782128.88102551945</v>
@@ -2855,10 +2858,10 @@
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B65" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2924,7 +2927,7 @@
         <v>17</v>
       </c>
       <c r="AF65" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG65">
         <v>716582.30967593449</v>
@@ -2935,7 +2938,7 @@
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -3001,7 +3004,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG66">
         <v>490934.33413928538</v>
@@ -3012,22 +3015,22 @@
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D67" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E67" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G67" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H67" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -3078,7 +3081,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG67">
         <v>384844.65214466688</v>
@@ -3089,7 +3092,7 @@
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D68">
         <v>25118</v>
@@ -3155,7 +3158,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG68">
         <v>355269.41910118907</v>
@@ -3166,72 +3169,72 @@
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D70" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E70" t="s">
+        <v>94</v>
+      </c>
+      <c r="F70" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" t="s">
+        <v>36</v>
+      </c>
+      <c r="H70" t="s">
+        <v>40</v>
+      </c>
+      <c r="J70" t="s">
         <v>93</v>
       </c>
-      <c r="F70" t="s">
-        <v>25</v>
-      </c>
-      <c r="G70" t="s">
-        <v>34</v>
-      </c>
-      <c r="H70" t="s">
-        <v>38</v>
-      </c>
-      <c r="J70" t="s">
-        <v>92</v>
-      </c>
       <c r="K70" t="s">
+        <v>94</v>
+      </c>
+      <c r="L70" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" t="s">
+        <v>36</v>
+      </c>
+      <c r="N70" t="s">
+        <v>40</v>
+      </c>
+      <c r="P70" t="s">
         <v>93</v>
       </c>
-      <c r="L70" t="s">
-        <v>25</v>
-      </c>
-      <c r="M70" t="s">
-        <v>34</v>
-      </c>
-      <c r="N70" t="s">
-        <v>38</v>
-      </c>
-      <c r="P70" t="s">
-        <v>92</v>
-      </c>
       <c r="Q70" t="s">
+        <v>94</v>
+      </c>
+      <c r="R70" t="s">
+        <v>26</v>
+      </c>
+      <c r="S70" t="s">
+        <v>36</v>
+      </c>
+      <c r="T70" t="s">
+        <v>40</v>
+      </c>
+      <c r="V70" t="s">
         <v>93</v>
       </c>
-      <c r="R70" t="s">
-        <v>25</v>
-      </c>
-      <c r="S70" t="s">
-        <v>34</v>
-      </c>
-      <c r="T70" t="s">
-        <v>38</v>
-      </c>
-      <c r="V70" t="s">
-        <v>92</v>
-      </c>
       <c r="W70" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y70" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z70" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3296,7 +3299,7 @@
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D72">
         <v>73</v>
@@ -3361,7 +3364,7 @@
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3426,7 +3429,7 @@
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D74">
         <v>152</v>
@@ -3491,7 +3494,7 @@
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3556,7 +3559,7 @@
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D76">
         <v>117</v>
@@ -3621,7 +3624,7 @@
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3686,7 +3689,7 @@
     </row>
     <row r="78" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3751,7 +3754,7 @@
     </row>
     <row r="79" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3816,7 +3819,7 @@
     </row>
     <row r="80" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3881,7 +3884,7 @@
     </row>
     <row r="81" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3946,7 +3949,7 @@
     </row>
     <row r="82" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -4011,10 +4014,10 @@
     </row>
     <row r="83" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B83" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -4079,7 +4082,7 @@
     </row>
     <row r="84" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -4144,22 +4147,22 @@
     </row>
     <row r="85" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D85" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E85" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G85" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H85" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -4209,7 +4212,7 @@
     </row>
     <row r="86" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D86">
         <v>342</v>
@@ -4274,72 +4277,72 @@
     </row>
     <row r="88" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D88" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E88" t="s">
+        <v>94</v>
+      </c>
+      <c r="F88" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" t="s">
+        <v>36</v>
+      </c>
+      <c r="H88" t="s">
+        <v>40</v>
+      </c>
+      <c r="J88" t="s">
         <v>93</v>
       </c>
-      <c r="F88" t="s">
-        <v>25</v>
-      </c>
-      <c r="G88" t="s">
-        <v>34</v>
-      </c>
-      <c r="H88" t="s">
-        <v>38</v>
-      </c>
-      <c r="J88" t="s">
-        <v>92</v>
-      </c>
       <c r="K88" t="s">
+        <v>94</v>
+      </c>
+      <c r="L88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" t="s">
+        <v>36</v>
+      </c>
+      <c r="N88" t="s">
+        <v>40</v>
+      </c>
+      <c r="P88" t="s">
         <v>93</v>
       </c>
-      <c r="L88" t="s">
-        <v>25</v>
-      </c>
-      <c r="M88" t="s">
-        <v>34</v>
-      </c>
-      <c r="N88" t="s">
-        <v>38</v>
-      </c>
-      <c r="P88" t="s">
-        <v>92</v>
-      </c>
       <c r="Q88" t="s">
+        <v>94</v>
+      </c>
+      <c r="R88" t="s">
+        <v>26</v>
+      </c>
+      <c r="S88" t="s">
+        <v>36</v>
+      </c>
+      <c r="T88" t="s">
+        <v>40</v>
+      </c>
+      <c r="V88" t="s">
         <v>93</v>
       </c>
-      <c r="R88" t="s">
-        <v>25</v>
-      </c>
-      <c r="S88" t="s">
-        <v>34</v>
-      </c>
-      <c r="T88" t="s">
-        <v>38</v>
-      </c>
-      <c r="V88" t="s">
-        <v>92</v>
-      </c>
       <c r="W88" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y88" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z88" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -4404,7 +4407,7 @@
     </row>
     <row r="90" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D90">
         <v>19072</v>
@@ -4469,7 +4472,7 @@
     </row>
     <row r="91" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -4534,7 +4537,7 @@
     </row>
     <row r="92" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D92">
         <v>152</v>
@@ -4599,7 +4602,7 @@
     </row>
     <row r="93" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -4664,7 +4667,7 @@
     </row>
     <row r="94" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D94">
         <v>2868</v>
@@ -4729,7 +4732,7 @@
     </row>
     <row r="95" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -4794,7 +4797,7 @@
     </row>
     <row r="96" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -4859,7 +4862,7 @@
     </row>
     <row r="97" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -4924,7 +4927,7 @@
     </row>
     <row r="98" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D98">
         <v>207</v>
@@ -4989,7 +4992,7 @@
     </row>
     <row r="99" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D99">
         <v>3161</v>
@@ -5054,7 +5057,7 @@
     </row>
     <row r="100" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -5119,10 +5122,10 @@
     </row>
     <row r="101" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -5187,7 +5190,7 @@
     </row>
     <row r="102" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -5252,22 +5255,22 @@
     </row>
     <row r="103" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -5317,7 +5320,7 @@
     </row>
     <row r="104" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D104">
         <v>25460</v>
@@ -5382,7 +5385,7 @@
     </row>
     <row r="106" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H106">
         <v>-4</v>
@@ -5390,7 +5393,7 @@
     </row>
     <row r="108" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H108">
         <v>1590177</v>
